--- a/excel/pandas/codigos/productos_con_barras.xlsx
+++ b/excel/pandas/codigos/productos_con_barras.xlsx
@@ -1,128 +1,3 @@
-
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
@@ -147,6 +22,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -172,6 +50,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -197,6 +78,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -222,6 +106,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -247,6 +134,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -272,6 +162,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -297,6 +190,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -322,6 +218,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -347,6 +246,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -372,6 +274,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -397,6 +302,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -422,6 +330,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -447,6 +358,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -472,6 +386,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -497,6 +414,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -522,6 +442,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -547,6 +470,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -572,6 +498,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,6 +526,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -622,6 +554,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -647,6 +582,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -672,6 +610,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -697,6 +638,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -722,6 +666,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -747,6 +694,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -772,6 +722,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -797,6 +750,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -822,6 +778,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -847,6 +806,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -872,6 +834,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -897,6 +862,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -922,6 +890,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -947,6 +918,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -972,6 +946,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -997,6 +974,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1022,6 +1002,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1047,6 +1030,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1072,6 +1058,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1097,6 +1086,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1122,6 +1114,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1147,6 +1142,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1172,6 +1170,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1197,6 +1198,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1222,6 +1226,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1247,6 +1254,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1272,6 +1282,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1297,6 +1310,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1322,6 +1338,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1347,6 +1366,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1372,6 +1394,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1397,6 +1422,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1422,6 +1450,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1447,6 +1478,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1472,6 +1506,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1497,6 +1534,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1522,6 +1562,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1547,6 +1590,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1572,6 +1618,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1597,6 +1646,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1622,6 +1674,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1647,6 +1702,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1672,6 +1730,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1697,6 +1758,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1722,6 +1786,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1747,6 +1814,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1772,6 +1842,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1797,6 +1870,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1822,6 +1898,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1847,6 +1926,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1872,6 +1954,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1897,6 +1982,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1922,6 +2010,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1947,6 +2038,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1972,6 +2066,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1997,6 +2094,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2022,6 +2122,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2047,6 +2150,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2072,6 +2178,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2097,6 +2206,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2122,6 +2234,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2147,6 +2262,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2172,6 +2290,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2197,6 +2318,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2222,6 +2346,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2247,6 +2374,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2272,6 +2402,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2297,6 +2430,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2322,6 +2458,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2347,6 +2486,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2372,6 +2514,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2391,6 +2536,2284 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId110"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId111"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="115" name="Image 115" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId115"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="116" name="Image 116" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId116"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="118" name="Image 118" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId118"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="119" name="Image 119" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId119"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="120" name="Image 120" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="122" name="Image 122" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId122"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="123" name="Image 123" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId123"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="124" name="Image 124" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId124"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="125" name="Image 125" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId125"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="126" name="Image 126" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId126"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="127" name="Image 127" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId127"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="128" name="Image 128" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId128"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="129" name="Image 129" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId129"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="130" name="Image 130" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId130"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="131" name="Image 131" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId131"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="132" name="Image 132" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId132"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="133" name="Image 133" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId133"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="134" name="Image 134" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId134"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="135" name="Image 135" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId135"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="136" name="Image 136" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId136"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="137" name="Image 137" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId137"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="138" name="Image 138" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId138"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="139" name="Image 139" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId139"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="140" name="Image 140" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId140"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="141" name="Image 141" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId141"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="142" name="Image 142" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId142"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="143" name="Image 143" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId143"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="144" name="Image 144" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId144"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="145" name="Image 145" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId145"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>74</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="146" name="Image 146" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId146"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="147" name="Image 147" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId147"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="148" name="Image 148" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId148"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="149" name="Image 149" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId149"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="150" name="Image 150" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId150"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="151" name="Image 151" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId151"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="152" name="Image 152" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId152"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>81</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="153" name="Image 153" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId153"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>84</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="154" name="Image 154" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId154"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="155" name="Image 155" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId155"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="156" name="Image 156" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId156"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="157" name="Image 157" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId157"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="158" name="Image 158" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId158"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>91</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="159" name="Image 159" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId159"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>92</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="160" name="Image 160" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId160"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="161" name="Image 161" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId161"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="162" name="Image 162" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId162"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="163" name="Image 163" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId163"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="164" name="Image 164" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId164"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="165" name="Image 165" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId165"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="166" name="Image 166" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="167" name="Image 167" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId167"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="168" name="Image 168" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId168"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="169" name="Image 169" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId169"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="170" name="Image 170" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId170"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="171" name="Image 171" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId171"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="172" name="Image 172" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId172"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="173" name="Image 173" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId173"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="174" name="Image 174" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId174"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>113</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="175" name="Image 175" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId175"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="176" name="Image 176" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId176"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="177" name="Image 177" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId177"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>116</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="178" name="Image 178" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId178"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="179" name="Image 179" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId179"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>118</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="180" name="Image 180" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId180"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>119</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="181" name="Image 181" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId181"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>120</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1714500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="182" name="Image 182" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId182"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2693,9 +5116,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D121"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -2772,6 +5196,9 @@
       </c>
       <c r="B9" t="n">
         <v>5500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>50</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4199,4 +6626,84 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stock anterior</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Stock resultante</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46252.47716783312</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>100000000003</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pechuga</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ENTRADA</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>